--- a/data/gravel/Bombtrack Beyond+ 2025.xlsx
+++ b/data/gravel/Bombtrack Beyond+ 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA833B5C-4EDC-A94E-9B15-3E45259C24C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3605B56-CD23-7942-BDB5-8F6057840116}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10180" yWindow="1480" windowWidth="17740" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30840" yWindow="-21460" windowWidth="17740" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="110">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="111">
   <si>
     <t>brand</t>
   </si>
@@ -363,6 +363,9 @@
   </si>
   <si>
     <t>a8:f33</t>
+  </si>
+  <si>
+    <t>https://images.squarespace-cdn.com/content/v1/60d2d479d2b7b75136ea090c/1753270933143-CPF93IVV5ELER1LG2E63/Bombtrack_Beyond%2B_29_matt_sage_4055822552363_web_1.jpg</t>
   </si>
 </sst>
 </file>
@@ -748,6 +751,11 @@
         <v>103</v>
       </c>
     </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>110</v>
+      </c>
+    </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>

--- a/data/gravel/Bombtrack Beyond+ 2025.xlsx
+++ b/data/gravel/Bombtrack Beyond+ 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3605B56-CD23-7942-BDB5-8F6057840116}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4159CB34-11D1-8A42-93B7-3FFE41C71E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30840" yWindow="-21460" windowWidth="17740" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="113">
   <si>
     <t>brand</t>
   </si>
@@ -366,6 +366,12 @@
   </si>
   <si>
     <t>https://images.squarespace-cdn.com/content/v1/60d2d479d2b7b75136ea090c/1753270933143-CPF93IVV5ELER1LG2E63/Bombtrack_Beyond%2B_29_matt_sage_4055822552363_web_1.jpg</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Cologne, Germany</t>
   </si>
 </sst>
 </file>
@@ -705,7 +711,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H73"/>
+  <dimension ref="A1:H74"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1534,6 +1540,14 @@
         <v>86</v>
       </c>
     </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>111</v>
+      </c>
+      <c r="B74" t="s">
+        <v>112</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Bombtrack Beyond+ 2025.xlsx
+++ b/data/gravel/Bombtrack Beyond+ 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4159CB34-11D1-8A42-93B7-3FFE41C71E11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD076769-CF32-8C4F-A244-ECC750FFB5F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="30840" yWindow="-21460" windowWidth="17740" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="119">
   <si>
     <t>brand</t>
   </si>
@@ -372,6 +372,24 @@
   </si>
   <si>
     <t>Cologne, Germany</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -711,7 +729,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:H80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1371,180 +1389,210 @@
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>63</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>64</v>
+        <v>114</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>65</v>
-      </c>
-      <c r="B52">
-        <v>30.9</v>
+        <v>115</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>66</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>107</v>
+        <v>116</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>67</v>
-      </c>
-      <c r="B54">
-        <v>32</v>
+        <v>117</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>68</v>
+        <v>118</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>69</v>
-      </c>
-      <c r="B56">
-        <v>200</v>
+        <v>63</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>70</v>
-      </c>
-      <c r="B57">
-        <v>180</v>
+        <v>64</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>71</v>
-      </c>
-      <c r="B58" s="1" t="s">
-        <v>99</v>
+        <v>65</v>
+      </c>
+      <c r="B58">
+        <v>30.9</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>73</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>97</v>
+        <v>67</v>
+      </c>
+      <c r="B60">
+        <v>32</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>74</v>
-      </c>
-      <c r="B61" s="1" t="s">
-        <v>97</v>
+        <v>68</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>75</v>
+        <v>69</v>
+      </c>
+      <c r="B62">
+        <v>200</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="B63">
-        <v>2</v>
+        <v>180</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>77</v>
-      </c>
-      <c r="B64">
-        <v>1</v>
+        <v>71</v>
+      </c>
+      <c r="B64" s="1" t="s">
+        <v>99</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>78</v>
-      </c>
-      <c r="B65" s="1">
-        <v>1</v>
+        <v>72</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>79</v>
-      </c>
-      <c r="B66" s="1">
-        <v>3</v>
+        <v>73</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>80</v>
+        <v>74</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>88</v>
+        <v>97</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>81</v>
-      </c>
-      <c r="B68" s="1" t="s">
-        <v>88</v>
+        <v>75</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>82</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>88</v>
+        <v>76</v>
+      </c>
+      <c r="B69">
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>83</v>
+        <v>77</v>
+      </c>
+      <c r="B70">
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>84</v>
+        <v>78</v>
+      </c>
+      <c r="B71" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>85</v>
+        <v>79</v>
+      </c>
+      <c r="B72" s="1">
+        <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>86</v>
+        <v>80</v>
+      </c>
+      <c r="B73" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
+        <v>81</v>
+      </c>
+      <c r="B74" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>82</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A78" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A79" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A80" t="s">
         <v>111</v>
       </c>
-      <c r="B74" t="s">
+      <c r="B80" t="s">
         <v>112</v>
       </c>
     </row>

--- a/data/gravel/Bombtrack Beyond+ 2025.xlsx
+++ b/data/gravel/Bombtrack Beyond+ 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD076769-CF32-8C4F-A244-ECC750FFB5F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{959DC2C2-09EF-ED48-BF10-0431A9357DD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30840" yWindow="-21460" windowWidth="17740" windowHeight="15480" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9020" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="122">
   <si>
     <t>brand</t>
   </si>
@@ -362,9 +362,6 @@
     <t>flat bar</t>
   </si>
   <si>
-    <t>a8:f33</t>
-  </si>
-  <si>
     <t>https://images.squarespace-cdn.com/content/v1/60d2d479d2b7b75136ea090c/1753270933143-CPF93IVV5ELER1LG2E63/Bombtrack_Beyond%2B_29_matt_sage_4055822552363_web_1.jpg</t>
   </si>
   <si>
@@ -390,6 +387,18 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>fork_travel</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
+  </si>
+  <si>
+    <t>a8:f35</t>
+  </si>
+  <si>
+    <t>https://www.seido-components.com/products/bps-fork#:~:text=Built%20to%20withstand%20the%20most%20unforgiving%20conditions%2C,can%20fit%20a%20huge%20variety%20of%20bikes</t>
   </si>
 </sst>
 </file>
@@ -729,7 +738,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H80"/>
+  <dimension ref="A1:H82"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -777,7 +786,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -785,7 +794,7 @@
         <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>109</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -969,7 +978,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>23</v>
       </c>
@@ -989,7 +998,7 @@
         <v>450</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>25</v>
       </c>
@@ -1009,7 +1018,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>27</v>
       </c>
@@ -1029,7 +1038,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>29</v>
       </c>
@@ -1049,7 +1058,7 @@
         <v>1188</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>31</v>
       </c>
@@ -1069,7 +1078,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>33</v>
       </c>
@@ -1089,7 +1098,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>35</v>
       </c>
@@ -1109,7 +1118,7 @@
         <v>653</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>37</v>
       </c>
@@ -1129,7 +1138,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>87</v>
       </c>
@@ -1148,421 +1157,445 @@
       <c r="F25">
         <v>500</v>
       </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" t="s">
+      <c r="G25" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A26" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C26">
+        <v>0</v>
+      </c>
+      <c r="D26">
+        <v>0</v>
+      </c>
+      <c r="E26">
+        <v>0</v>
+      </c>
+      <c r="F26">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A27" s="1" t="s">
+        <v>119</v>
+      </c>
+      <c r="C27">
+        <v>0</v>
+      </c>
+      <c r="D27">
+        <v>0</v>
+      </c>
+      <c r="E27">
+        <v>0</v>
+      </c>
+      <c r="F27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A28" t="s">
         <v>43</v>
       </c>
-      <c r="D26">
+      <c r="D28">
         <v>2910</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" t="s">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A29" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" t="s">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A30" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" t="s">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A31" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" t="s">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A32" t="s">
         <v>46</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B32" t="s">
         <v>46</v>
       </c>
-      <c r="C30">
+      <c r="C32">
         <v>2.6</v>
       </c>
-      <c r="D30">
+      <c r="D32">
         <v>2.6</v>
       </c>
-      <c r="E30">
+      <c r="E32">
         <v>2.6</v>
       </c>
-      <c r="F30">
+      <c r="F32">
         <v>2.6</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" t="s">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A33" t="s">
         <v>47</v>
       </c>
-      <c r="B31" t="s">
+      <c r="B33" t="s">
         <v>47</v>
       </c>
-      <c r="C31">
+      <c r="C33">
         <v>3</v>
       </c>
-      <c r="D31">
+      <c r="D33">
         <v>3</v>
       </c>
-      <c r="E31">
+      <c r="E33">
         <v>3</v>
       </c>
-      <c r="F31">
+      <c r="F33">
         <v>3</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" t="s">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A34" t="s">
         <v>48</v>
       </c>
-      <c r="C32">
-        <f t="shared" ref="C32:E33" si="0">C34/10</f>
+      <c r="C34">
+        <f t="shared" ref="C34:E35" si="0">C36/10</f>
         <v>160</v>
       </c>
-      <c r="D32">
+      <c r="D34">
         <f t="shared" si="0"/>
         <v>170</v>
       </c>
-      <c r="E32">
+      <c r="E34">
         <f t="shared" si="0"/>
         <v>179</v>
       </c>
-      <c r="F32">
-        <f t="shared" ref="F32" si="1">F34/10</f>
+      <c r="F34">
+        <f t="shared" ref="F34" si="1">F36/10</f>
         <v>188</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A33" t="s">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A35" t="s">
         <v>49</v>
       </c>
-      <c r="C33">
+      <c r="C35">
         <f t="shared" si="0"/>
         <v>171</v>
       </c>
-      <c r="D33">
+      <c r="D35">
         <f t="shared" si="0"/>
         <v>181</v>
       </c>
-      <c r="E33">
+      <c r="E35">
         <f t="shared" si="0"/>
         <v>190</v>
       </c>
-      <c r="F33">
-        <f t="shared" ref="F33" si="2">F35/10</f>
+      <c r="F35">
+        <f t="shared" ref="F35" si="2">F37/10</f>
         <v>199</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="C34">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="C36">
         <v>1600</v>
       </c>
-      <c r="D34">
+      <c r="D36">
         <v>1700</v>
       </c>
-      <c r="E34">
+      <c r="E36">
         <v>1790</v>
       </c>
-      <c r="F34">
+      <c r="F36">
         <v>1880</v>
       </c>
-      <c r="H34" t="s">
+      <c r="H36" t="s">
         <v>95</v>
-      </c>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A35" t="s">
-        <v>50</v>
-      </c>
-      <c r="B35" t="s">
-        <v>51</v>
-      </c>
-      <c r="C35">
-        <v>1710</v>
-      </c>
-      <c r="D35">
-        <v>1810</v>
-      </c>
-      <c r="E35">
-        <v>1900</v>
-      </c>
-      <c r="F35">
-        <v>1990</v>
-      </c>
-      <c r="H35" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A36" t="s">
-        <v>89</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>90</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>108</v>
+        <v>50</v>
+      </c>
+      <c r="B37" t="s">
+        <v>51</v>
+      </c>
+      <c r="C37">
+        <v>1710</v>
+      </c>
+      <c r="D37">
+        <v>1810</v>
+      </c>
+      <c r="E37">
+        <v>1900</v>
+      </c>
+      <c r="F37">
+        <v>1990</v>
+      </c>
+      <c r="H37" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>52</v>
+        <v>90</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>53</v>
-      </c>
-      <c r="B40" s="1"/>
+        <v>91</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>54</v>
+        <v>52</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>55</v>
-      </c>
-      <c r="B42">
-        <v>3</v>
-      </c>
+        <v>53</v>
+      </c>
+      <c r="B42" s="1"/>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>56</v>
-      </c>
-      <c r="C43" s="1"/>
+        <v>54</v>
+      </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>57</v>
+        <v>55</v>
+      </c>
+      <c r="B44">
+        <v>3</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>58</v>
-      </c>
+        <v>56</v>
+      </c>
+      <c r="C45" s="1"/>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>59</v>
+        <v>57</v>
+      </c>
+      <c r="B46">
+        <v>120</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>61</v>
-      </c>
-      <c r="B48">
-        <v>148</v>
+        <v>59</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>62</v>
-      </c>
-      <c r="B49">
-        <v>110</v>
+        <v>60</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>113</v>
+        <v>61</v>
+      </c>
+      <c r="B50">
+        <v>148</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>114</v>
+        <v>62</v>
+      </c>
+      <c r="B51">
+        <v>110</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>63</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>106</v>
+        <v>116</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>64</v>
+        <v>117</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>65</v>
-      </c>
-      <c r="B58">
-        <v>30.9</v>
+        <v>63</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>66</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>107</v>
+        <v>64</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="B60">
-        <v>32</v>
+        <v>30.9</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>68</v>
+        <v>66</v>
+      </c>
+      <c r="B61" s="1" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="B62">
-        <v>200</v>
+        <v>32</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>70</v>
-      </c>
-      <c r="B63">
-        <v>180</v>
+        <v>68</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>71</v>
-      </c>
-      <c r="B64" s="1" t="s">
-        <v>99</v>
+        <v>69</v>
+      </c>
+      <c r="B64">
+        <v>200</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>72</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>100</v>
+        <v>70</v>
+      </c>
+      <c r="B65">
+        <v>180</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>75</v>
+        <v>73</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>76</v>
-      </c>
-      <c r="B69">
-        <v>2</v>
+        <v>74</v>
+      </c>
+      <c r="B69" s="1" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>77</v>
-      </c>
-      <c r="B70">
-        <v>1</v>
+        <v>75</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>78</v>
-      </c>
-      <c r="B71" s="1">
-        <v>1</v>
+        <v>76</v>
+      </c>
+      <c r="B71">
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>79</v>
-      </c>
-      <c r="B72" s="1">
-        <v>3</v>
+        <v>77</v>
+      </c>
+      <c r="B72">
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
-        <v>80</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>88</v>
+        <v>78</v>
+      </c>
+      <c r="B73" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
-        <v>81</v>
-      </c>
-      <c r="B74" s="1" t="s">
-        <v>88</v>
+        <v>79</v>
+      </c>
+      <c r="B74" s="1">
+        <v>3</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>88</v>
@@ -1570,30 +1603,46 @@
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>83</v>
+        <v>81</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>84</v>
+        <v>82</v>
+      </c>
+      <c r="B77" s="1" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A81" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A82" t="s">
+        <v>110</v>
+      </c>
+      <c r="B82" t="s">
         <v>111</v>
-      </c>
-      <c r="B80" t="s">
-        <v>112</v>
       </c>
     </row>
   </sheetData>
